--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_380_R38.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_380_R38.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>10.8753</v>
+        <v>7.2968</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0374</v>
+        <v>3.635</v>
       </c>
       <c r="F2" t="n">
-        <v>4.838</v>
+        <v>3.6618</v>
       </c>
       <c r="G2" t="n">
         <v>3.4594</v>
@@ -610,13 +610,13 @@
         <v>2.3195</v>
       </c>
       <c r="S2" t="n">
-        <v>6.524</v>
+        <v>2.9455</v>
       </c>
       <c r="T2" t="n">
-        <v>4.5415</v>
+        <v>2.1392</v>
       </c>
       <c r="U2" t="n">
-        <v>1.9826</v>
+        <v>0.8063</v>
       </c>
       <c r="V2" t="n">
         <v>1.3558</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0599</v>
+        <v>6.1386</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7503</v>
+        <v>5.9299</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3095</v>
+        <v>0.2087</v>
       </c>
       <c r="G3" t="n">
         <v>6.0994</v>
@@ -688,13 +688,13 @@
         <v>1.6237</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1839</v>
+        <v>-0.1052</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9709</v>
+        <v>0.2087</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2131</v>
+        <v>-0.3139</v>
       </c>
       <c r="V3" t="n">
         <v>1.0722</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5024999999999999</v>
+        <v>0.8296</v>
       </c>
       <c r="E4" t="n">
-        <v>1.0094</v>
+        <v>1.202</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.5069</v>
+        <v>-0.3725</v>
       </c>
       <c r="G4" t="n">
         <v>0.1654</v>
@@ -766,13 +766,13 @@
         <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1448</v>
+        <v>-0.8178</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0351</v>
+        <v>0.1575</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.1097</v>
+        <v>-0.9752</v>
       </c>
       <c r="V4" t="n">
         <v>-0.1418</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2318</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1677</v>
+        <v>-1.5955</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0641</v>
+        <v>1.604</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.2737</v>
+        <v>-1.3541</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.474</v>
+        <v>-1.0229</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.7997</v>
+        <v>-0.3312</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.3414</v>
+        <v>-2.2011</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.7023</v>
+        <v>-1.4516</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6391</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0678</v>
+        <v>0.847</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2283</v>
+        <v>0.4287</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1605</v>
+        <v>0.4183</v>
       </c>
       <c r="P5" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S5" t="n">
-        <v>1.2735</v>
+        <v>0.11</v>
       </c>
       <c r="T5" t="n">
-        <v>1.6869</v>
+        <v>0.6056</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4134</v>
+        <v>-0.4955</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
       <c r="W5" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.214</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. BUTKEVICIUS</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0619</v>
+        <v>-0.0587</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3974</v>
+        <v>-0.0218</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4593</v>
+        <v>-0.0369</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.545</v>
+        <v>-2.2764</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5295</v>
+        <v>-1.905</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.0745</v>
+        <v>-0.3714</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.1298</v>
+        <v>-1.8152</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1547</v>
+        <v>-1.9221</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2845</v>
+        <v>0.1069</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4152</v>
+        <v>-0.4612</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3748</v>
+        <v>0.0171</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.79</v>
+        <v>-0.4783</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1598</v>
+        <v>1.8556</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5553</v>
+        <v>0.2899</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7591</v>
+        <v>0.6491</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2038</v>
+        <v>-0.3591</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.6083</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>A. BUTKEVICIUS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1095</v>
+        <v>-0.3754</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7135</v>
+        <v>-0.1177</v>
       </c>
       <c r="F7" t="n">
-        <v>1.604</v>
+        <v>-0.2577</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.3541</v>
+        <v>-1.545</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.0229</v>
+        <v>0.5295</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3312</v>
+        <v>-2.0745</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.2011</v>
+        <v>-0.1298</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.4516</v>
+        <v>0.1547</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.2845</v>
       </c>
       <c r="M7" t="n">
-        <v>0.847</v>
+        <v>-1.4152</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4287</v>
+        <v>0.3748</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4183</v>
+        <v>-1.79</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.2418</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4876</v>
+        <v>0.244</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4955</v>
+        <v>-0.0022</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8507</v>
+        <v>-0.4766</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8474</v>
+        <v>-0.7759</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0033</v>
+        <v>0.2993</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2764</v>
+        <v>-1.2737</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.905</v>
+        <v>-0.474</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3714</v>
+        <v>-0.7997</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.8152</v>
+        <v>-1.3414</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.9221</v>
+        <v>-0.7023</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1069</v>
+        <v>-0.6391</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4612</v>
+        <v>0.0678</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0171</v>
+        <v>0.2283</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4783</v>
+        <v>-0.1605</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3917</v>
+        <v>0.232</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.4639</v>
+        <v>-1.3917</v>
       </c>
       <c r="R8" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5021</v>
+        <v>0.5652</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1766</v>
+        <v>0.7433</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3255</v>
+        <v>-0.1781</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6083</v>
+        <v>1.214</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>D. GIEDRAITIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8861</v>
+        <v>-1.3362</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4143</v>
+        <v>-2.0587</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3004</v>
+        <v>0.7224</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2609</v>
+        <v>-0.1312</v>
       </c>
       <c r="H9" t="n">
-        <v>0.2749</v>
+        <v>0.1465</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5358</v>
+        <v>-0.2777</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1507</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0035</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1472</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4116</v>
+        <v>0.6183</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2714</v>
+        <v>0.1465</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.683</v>
+        <v>0.4718</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3747</v>
+        <v>-0.5091</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2636</v>
+        <v>-0.1494</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1111</v>
+        <v>-0.3598</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. GIEDRAITIS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.4035</v>
+        <v>-1.3915</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0587</v>
+        <v>-0.0575</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6552</v>
+        <v>-1.334</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1312</v>
+        <v>-1.2609</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1465</v>
+        <v>0.2749</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2777</v>
+        <v>-1.5358</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.1507</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.0035</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.7495000000000001</v>
+        <v>0.1472</v>
       </c>
       <c r="M10" t="n">
-        <v>0.6183</v>
+        <v>-1.4116</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1465</v>
+        <v>0.2714</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4718</v>
+        <v>-1.683</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.6959</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5764</v>
+        <v>-0.1307</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1494</v>
+        <v>-0.2082</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.427</v>
+        <v>0.0775</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.4609</v>
+        <v>-1.9042</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.2543</v>
+        <v>-2.0001</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2066</v>
+        <v>0.0959</v>
       </c>
       <c r="G11" t="n">
         <v>0.76</v>
@@ -1312,13 +1312,13 @@
         <v>2.3195</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.739</v>
+        <v>-1.1824</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.5604</v>
+        <v>-0.3062</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1786</v>
+        <v>-0.8762</v>
       </c>
       <c r="V11" t="n">
         <v>0.1418</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.8246</v>
+        <v>-3.2851</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9608</v>
+        <v>-4.8245</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1362</v>
+        <v>1.5394</v>
       </c>
       <c r="G12" t="n">
         <v>-3.6429</v>
@@ -1390,13 +1390,13 @@
         <v>1.6237</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.2539</v>
+        <v>1.2856</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0272</v>
+        <v>1.109</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2267</v>
+        <v>0.1766</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.072299999999998</v>
+        <v>5.445800000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.0582</v>
+        <v>-0.6848000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>6.1305</v>
+        <v>6.130400000000002</v>
       </c>
       <c r="G13" t="n">
-        <v>-1</v>
+        <v>-1.000000000000001</v>
       </c>
       <c r="H13" t="n">
         <v>5.5583</v>
@@ -1447,10 +1447,10 @@
         <v>1.9182</v>
       </c>
       <c r="L13" t="n">
-        <v>1.8893</v>
+        <v>1.889299999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.807499999999999</v>
+        <v>-4.8075</v>
       </c>
       <c r="N13" t="n">
         <v>3.64</v>
@@ -1468,10 +1468,10 @@
         <v>15.077</v>
       </c>
       <c r="S13" t="n">
-        <v>2.319500000000001</v>
+        <v>2.692800000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>4.819100000000001</v>
+        <v>5.192600000000001</v>
       </c>
       <c r="U13" t="n">
         <v>-2.4996</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.6481</v>
+        <v>5.6145</v>
       </c>
       <c r="E14" t="n">
         <v>4.5178</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1303</v>
+        <v>1.0967</v>
       </c>
       <c r="G14" t="n">
         <v>4.668</v>
@@ -1546,13 +1546,13 @@
         <v>1.8556</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8754999999999999</v>
+        <v>-0.9091</v>
       </c>
       <c r="T14" t="n">
         <v>-0.0861</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.7894</v>
+        <v>-0.823</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.6429</v>
+        <v>3.9353</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8931</v>
+        <v>2.129</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7498</v>
+        <v>1.8062</v>
       </c>
       <c r="G15" t="n">
         <v>5.1923</v>
@@ -1624,13 +1624,13 @@
         <v>2.0876</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0742</v>
+        <v>0.3666</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2047</v>
+        <v>0.4406</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1305</v>
+        <v>-0.074</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9716</v>
+        <v>2.3647</v>
       </c>
       <c r="E16" t="n">
-        <v>2.2633</v>
+        <v>1.5555</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7083</v>
+        <v>0.8091</v>
       </c>
       <c r="G16" t="n">
         <v>0.9424</v>
@@ -1702,13 +1702,13 @@
         <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>0.8694</v>
+        <v>0.2625</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6844</v>
+        <v>-0.0233</v>
       </c>
       <c r="U16" t="n">
-        <v>0.185</v>
+        <v>0.2858</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. DOKOSSI</t>
+          <t>D. WILLIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5868</v>
+        <v>0.5362</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0675</v>
+        <v>1.0158</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5194</v>
+        <v>-0.4795</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9025</v>
+        <v>0.4434</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3805</v>
+        <v>0.9988</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5221</v>
+        <v>-0.5553</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0456</v>
+        <v>0.7756999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3095</v>
+        <v>0.5917</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7361</v>
+        <v>0.184</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.143</v>
+        <v>-0.3322</v>
       </c>
       <c r="N17" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.4071</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.214</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.5515</v>
+        <v>-0.232</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3079</v>
+        <v>0.4512</v>
       </c>
       <c r="T17" t="n">
-        <v>1.2898</v>
+        <v>0.472</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.9818</v>
+        <v>-0.0209</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5361</v>
+        <v>-1.7501</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2525</v>
+        <v>-1.7501</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. WILLIS</t>
+          <t>A. DOKOSSI</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.2946</v>
+        <v>0.4568</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8978</v>
+        <v>-0.5223</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6032</v>
+        <v>0.9791</v>
       </c>
       <c r="G18" t="n">
-        <v>0.4434</v>
+        <v>0.9025</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9988</v>
+        <v>0.3805</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5553</v>
+        <v>0.5221</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7756999999999999</v>
+        <v>1.0456</v>
       </c>
       <c r="K18" t="n">
-        <v>0.5917</v>
+        <v>0.3095</v>
       </c>
       <c r="L18" t="n">
-        <v>0.184</v>
+        <v>0.7361</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.3322</v>
+        <v>-0.143</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4071</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.214</v>
       </c>
       <c r="P18" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>-2.5515</v>
+      </c>
+      <c r="R18" t="n">
         <v>1.3917</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.6237</v>
-      </c>
       <c r="S18" t="n">
-        <v>0.2095</v>
+        <v>0.1779</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3541</v>
+        <v>0.7</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1445</v>
+        <v>-0.5221</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.7501</v>
+        <v>0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.7501</v>
+        <v>0.2525</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2898</v>
+        <v>0.1446</v>
       </c>
       <c r="E19" t="n">
         <v>0.4737</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1839</v>
+        <v>-0.3291</v>
       </c>
       <c r="G19" t="n">
         <v>0.2086</v>
@@ -1936,13 +1936,13 @@
         <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>0.7771</v>
+        <v>0.6319</v>
       </c>
       <c r="T19" t="n">
         <v>0.7275</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0496</v>
+        <v>-0.0955</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3304</v>
+        <v>-0.364</v>
       </c>
       <c r="E20" t="n">
         <v>-0.1415</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1888</v>
+        <v>-0.2224</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3589</v>
@@ -2014,13 +2014,13 @@
         <v>0.9278</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8992</v>
+        <v>-0.9328</v>
       </c>
       <c r="T20" t="n">
         <v>-0.2082</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6909999999999999</v>
+        <v>-0.7246</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. SHAHRVIN</t>
+          <t>A. M'BAYE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6491</v>
+        <v>-1.1983</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5493</v>
+        <v>-0.3777</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1984</v>
+        <v>-0.8206</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.1603</v>
+        <v>-1.5332</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.09</v>
+        <v>-0.5628</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0702</v>
+        <v>-0.9704</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.1782</v>
+        <v>-0.3819</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.215</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0368</v>
+        <v>-1.0709</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0179</v>
+        <v>-1.1513</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1249</v>
+        <v>-1.2518</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.107</v>
+        <v>0.1005</v>
       </c>
       <c r="P21" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.232</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3514</v>
+        <v>-0.4512</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7275</v>
+        <v>0.0042</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.376</v>
+        <v>-0.4553</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. HOMMES</t>
+          <t>E. SHAHRVIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2816</v>
+        <v>-1.2718</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.8426</v>
+        <v>0.1954</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.439</v>
+        <v>-1.4672</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4611</v>
+        <v>-0.1603</v>
       </c>
       <c r="H22" t="n">
-        <v>0.4778</v>
+        <v>-0.09</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0167</v>
+        <v>-0.0702</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0536</v>
+        <v>-0.1782</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0168</v>
+        <v>-0.215</v>
       </c>
       <c r="L22" t="n">
         <v>0.0368</v>
       </c>
       <c r="M22" t="n">
-        <v>0.4075</v>
+        <v>0.0179</v>
       </c>
       <c r="N22" t="n">
-        <v>0.461</v>
+        <v>0.1249</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.0535</v>
+        <v>-0.107</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6959</v>
+        <v>0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5614</v>
+        <v>-0.2713</v>
       </c>
       <c r="T22" t="n">
-        <v>0.2636</v>
+        <v>0.3736</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2978</v>
+        <v>-0.6449</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6083</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. M'BAYE</t>
+          <t>D. HOMMES</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.5858</v>
+        <v>-1.7191</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.7315</v>
+        <v>-1.0785</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8542</v>
+        <v>-0.6407</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.5332</v>
+        <v>0.4611</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5628</v>
+        <v>0.4778</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9704</v>
+        <v>-0.0167</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.3819</v>
+        <v>0.0536</v>
       </c>
       <c r="K23" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.0168</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.0709</v>
+        <v>0.0368</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1513</v>
+        <v>0.4075</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.2518</v>
+        <v>0.461</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1005</v>
+        <v>-0.0535</v>
       </c>
       <c r="P23" t="n">
-        <v>0.9278</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R23" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8386</v>
+        <v>0.1239</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3497</v>
+        <v>0.0277</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4889</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.1418</v>
+        <v>-1.6083</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.1418</v>
+        <v>-1.6083</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9587</v>
+        <v>-3.9492</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.6028</v>
+        <v>-4.131</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3559</v>
+        <v>0.1818</v>
       </c>
       <c r="G24" t="n">
         <v>-0.9339</v>
@@ -2326,13 +2326,13 @@
         <v>1.8556</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.4012</v>
+        <v>-1.3917</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-0.4007</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.5288</v>
+        <v>-0.9911</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.7005</v>
+        <v>-8.835599999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.4744</v>
+        <v>-9.7667</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7739</v>
+        <v>0.9311</v>
       </c>
       <c r="G25" t="n">
         <v>-8.8323</v>
@@ -2404,13 +2404,13 @@
         <v>1.8556</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.456</v>
+        <v>0.409</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.2355</v>
+        <v>0.4722</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.2205</v>
+        <v>-0.0633</v>
       </c>
       <c r="V25" t="n">
         <v>0.2836</v>
@@ -2437,16 +2437,16 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.072300000000002</v>
+        <v>-4.2859</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.1303</v>
+        <v>-6.130500000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>1.0583</v>
+        <v>1.8445</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9997000000000025</v>
+        <v>0.9997000000000007</v>
       </c>
       <c r="H26" t="n">
         <v>-5.558199999999999</v>
@@ -2482,13 +2482,13 @@
         <v>15.077</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.3196</v>
+        <v>-1.5331</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4996</v>
+        <v>2.4995</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.819</v>
+        <v>-4.032699999999999</v>
       </c>
       <c r="V26" t="n">
         <v>-3.7527</v>
@@ -2497,7 +2497,7 @@
         <v>1.6394</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.392100000000001</v>
+        <v>-5.392099999999999</v>
       </c>
     </row>
   </sheetData>
